--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,27 +1228,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124075141</v>
+        <v>137416281</v>
       </c>
       <c r="B7" t="n">
-        <v>58790</v>
+        <v>56765</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>206046</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1259,17 +1259,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Restenäs 270, Uddevalla, Boh</t>
+          <t>Restenäs, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317495</v>
+        <v>317508</v>
       </c>
       <c r="R7" t="n">
-        <v>6459123</v>
+        <v>6459047</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1293,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,6 +1333,108 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137416281</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124075141</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Restenäs 270, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>317495</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6459123</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124075141</t>
         </is>
@@ -1336,6 +1448,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103816074</v>
+        <v>137467131</v>
       </c>
       <c r="B4" t="n">
-        <v>89029</v>
+        <v>92410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,38 +899,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4392</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsvaxing agg.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uddevalla, Boh</t>
+          <t>Restenäs, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317537</v>
+        <v>317606</v>
       </c>
       <c r="R4" t="n">
-        <v>6459084</v>
+        <v>6459129</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,19 +953,29 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -985,65 +994,52 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103816074</t>
+          <t>https://artportalen.se/Sighting/137467131</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124668214</v>
+        <v>103816074</v>
       </c>
       <c r="B5" t="n">
-        <v>58209</v>
+        <v>89029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102980</v>
+        <v>4392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Restenäs 270, Uddevalla, Boh</t>
+          <t>Uddevalla, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317495</v>
+        <v>317537</v>
       </c>
       <c r="R5" t="n">
-        <v>6459123</v>
+        <v>6459084</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1070,29 +1066,19 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1111,16 +1097,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124668214</t>
+          <t>https://artportalen.se/Sighting/103816074</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121474818</v>
+        <v>124668214</v>
       </c>
       <c r="B6" t="n">
-        <v>58388</v>
+        <v>58209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,38 +1114,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>102980</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Turebacken, Boh</t>
+          <t>Restenäs 270, Uddevalla, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317562</v>
+        <v>317495</v>
       </c>
       <c r="R6" t="n">
-        <v>6459140</v>
+        <v>6459123</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1186,17 +1182,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stora flockar i trädtopparna.</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,16 +1223,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121474818</t>
+          <t>https://artportalen.se/Sighting/124668214</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137416281</v>
+        <v>121474818</v>
       </c>
       <c r="B7" t="n">
-        <v>56765</v>
+        <v>58388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,37 +1240,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206046</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Restenäs, Boh</t>
+          <t>Turebacken, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317508</v>
+        <v>317562</v>
       </c>
       <c r="R7" t="n">
-        <v>6459047</v>
+        <v>6459140</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,22 +1298,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stora flockar i trädtopparna.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,33 +1334,33 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137416281</t>
+          <t>https://artportalen.se/Sighting/121474818</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124075141</v>
+        <v>137416281</v>
       </c>
       <c r="B8" t="n">
-        <v>58790</v>
+        <v>56765</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>206046</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1371,17 +1371,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Restenäs 270, Uddevalla, Boh</t>
+          <t>Restenäs, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317495</v>
+        <v>317508</v>
       </c>
       <c r="R8" t="n">
-        <v>6459123</v>
+        <v>6459047</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,12 +1405,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,6 +1445,108 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137416281</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124075141</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Restenäs 270, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>317495</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6459123</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124075141</t>
         </is>
@@ -1449,6 +1561,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>137467131</v>
       </c>
       <c r="B4" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137416281</v>
       </c>
       <c r="B8" t="n">
-        <v>56765</v>
+        <v>56768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
